--- a/game-stats/Week1_Desert-Lions_vs_K2.xlsx
+++ b/game-stats/Week1_Desert-Lions_vs_K2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mostafa El-leboudi</t>
+          <t>Mostafa El-Leboudi</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1177,6 +1177,123 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Shafiq Said</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Ashkar</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alowaid</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,16 +1851,16 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Mohammed Aqrabawi</t>
+          <t>Ahmad Jaffal</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DL/WR</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -1773,16 +1890,16 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Jaffal</t>
+          <t>Ibrahim Ahmed</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -1812,16 +1929,16 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Ibrahim Ahmed</t>
+          <t>Yusuf Saleh</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>DB/WR</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -1851,16 +1968,16 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Yusuf Saleh</t>
+          <t>Aleem Abdulla</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>DB/WR</t>
+          <t>S/RB</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -1890,16 +2007,16 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aleem Abdulla</t>
+          <t>Jooma Abderazzaq</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>S/RB</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">

--- a/game-stats/Week1_Desert-Lions_vs_K2.xlsx
+++ b/game-stats/Week1_Desert-Lions_vs_K2.xlsx
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="13" t="n">

--- a/game-stats/Week1_Desert-Lions_vs_K2.xlsx
+++ b/game-stats/Week1_Desert-Lions_vs_K2.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -46,8 +46,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +71,14 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -108,11 +119,17 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -152,6 +169,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1505,13 +1528,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
     <col width="22" customWidth="1" style="16" min="2" max="2"/>
     <col width="14" customWidth="1" style="16" min="3" max="3"/>
     <col width="11" customWidth="1" style="16" min="4" max="18"/>
+    <col width="10" customWidth="1" style="16" min="16" max="16"/>
     <col width="8.710000000000001" customWidth="1" style="16" min="19" max="27"/>
   </cols>
   <sheetData>
@@ -1591,17 +1615,22 @@
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1655,13 +1684,16 @@
       <c r="O2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="13" t="n">
+      <c r="S2" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1713,13 +1745,16 @@
       <c r="O3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1771,13 +1806,16 @@
       <c r="O4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="R4" s="13" t="n">
+      <c r="S4" s="13" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1829,13 +1867,16 @@
       <c r="O5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1887,13 +1928,16 @@
       <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1945,13 +1989,16 @@
       <c r="O7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2003,13 +2050,16 @@
       <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2061,13 +2111,16 @@
       <c r="O9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="P9" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2119,13 +2172,16 @@
       <c r="O10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2177,13 +2233,16 @@
       <c r="O11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="P11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2235,13 +2294,16 @@
       <c r="O12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,13 +2355,16 @@
       <c r="O13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2351,13 +2416,16 @@
       <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2409,13 +2477,16 @@
       <c r="O15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2467,13 +2538,16 @@
       <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2525,13 +2599,16 @@
       <c r="O17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2583,13 +2660,16 @@
       <c r="O18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="P18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2641,13 +2721,16 @@
       <c r="O19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="P19" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3643,13 +3726,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
     <col width="22" customWidth="1" style="16" min="2" max="2"/>
     <col width="14" customWidth="1" style="16" min="3" max="3"/>
     <col width="11" customWidth="1" style="16" min="4" max="18"/>
+    <col width="10" customWidth="1" style="16" min="16" max="16"/>
     <col width="8.710000000000001" customWidth="1" style="16" min="19" max="27"/>
   </cols>
   <sheetData>
@@ -3729,17 +3813,22 @@
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -3793,13 +3882,16 @@
       <c r="O2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3851,13 +3943,16 @@
       <c r="O3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3909,13 +4004,16 @@
       <c r="O4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3967,13 +4065,16 @@
       <c r="O5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4025,13 +4126,16 @@
       <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4083,13 +4187,16 @@
       <c r="O7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4141,13 +4248,16 @@
       <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4199,13 +4309,16 @@
       <c r="O9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="P9" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4257,13 +4370,16 @@
       <c r="O10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4315,13 +4431,16 @@
       <c r="O11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="P11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4373,13 +4492,16 @@
       <c r="O12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4431,13 +4553,16 @@
       <c r="O13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4489,13 +4614,16 @@
       <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4547,13 +4675,16 @@
       <c r="O15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4605,13 +4736,16 @@
       <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4663,13 +4797,16 @@
       <c r="O17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4721,13 +4858,16 @@
       <c r="O18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="P18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week1_Desert-Lions_vs_K2.xlsx
+++ b/game-stats/Week1_Desert-Lions_vs_K2.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -175,6 +175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3726,7 +3727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -4481,13 +4482,13 @@
       </c>
       <c r="K12" s="13" t="n"/>
       <c r="L12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="15" t="n">
         <v>0</v>
@@ -4868,6 +4869,69 @@
         <v>0</v>
       </c>
       <c r="S18" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>49</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Terryon Taylor</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <v>68</v>
+      </c>
+      <c r="N19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="18" t="n">
         <v>0</v>
       </c>
     </row>
